--- a/tests/fixtures/template_minimal.xlsx
+++ b/tests/fixtures/template_minimal.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -79,8 +81,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -475,7 +478,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" style="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -486,7 +489,7 @@
   </cols>
   <sheetData>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Список выявленных недостатков информационной безопасности</t>
         </is>
@@ -494,47 +497,47 @@
     </row>
     <row r="4"/>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Объект тестирования</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Сегмент сети, из которого осуществлялась проверка</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Тип</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Описание</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Подробности</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Предлагаемые мероприятия</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
@@ -573,12 +576,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Сегмент сети</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Тип</t>
         </is>

--- a/tests/fixtures/template_minimal.xlsx
+++ b/tests/fixtures/template_minimal.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,10 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
     <font>
       <b val="1"/>
@@ -81,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -90,7 +94,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:I5"/>
+  <dimension ref="A3:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -542,6 +555,20 @@
           <t>Примечания</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7" hidden="1">
+      <c r="G7" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -576,12 +603,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Сегмент сети</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Тип</t>
         </is>
